--- a/data_lake/macro/China/GDP.xlsx
+++ b/data_lake/macro/China/GDP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\China\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/macro/China/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EDDCE88-3130-4D43-AB74-7CA6F512574A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25EC68E2-82FD-484F-A6F8-05A922D5206D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{7D3083A0-2A8D-45F5-BC69-B8C0E15D85EA}"/>
+    <workbookView xWindow="80" yWindow="780" windowWidth="19820" windowHeight="20800" activeTab="1" xr2:uid="{7D3083A0-2A8D-45F5-BC69-B8C0E15D85EA}"/>
   </bookViews>
   <sheets>
     <sheet name="info" sheetId="2" r:id="rId1"/>
@@ -109,11 +109,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="181" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="182" formatCode="0.0%"/>
-    <numFmt numFmtId="184" formatCode="yyyy/mm/dd;@"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -190,35 +189,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="184" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -233,10 +223,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="백분율" xfId="1" builtinId="5"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -252,9 +245,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -292,7 +285,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -398,7 +391,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -540,7 +533,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -549,51 +542,51 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{045BC4AA-E470-4F42-9D41-CBD385281723}">
   <dimension ref="B2:G3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="60" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="12" t="s">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="13">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B3" s="10">
         <v>1</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="10" t="s">
         <v>16</v>
       </c>
     </row>
@@ -606,19 +599,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E7E896-7AC3-4836-B145-CA85A39F0FCA}">
   <dimension ref="A1:G64"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
@@ -637,17 +630,17 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="11">
         <v>40543</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="11">
         <v>40563</v>
       </c>
-      <c r="C2" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D2" s="10" t="s">
+      <c r="C2" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="1">
@@ -660,17 +653,17 @@
         <v>9.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="11">
         <v>40633</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="11">
         <v>40648</v>
       </c>
-      <c r="C3" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D3" s="10" t="s">
+      <c r="C3" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="1">
@@ -683,17 +676,17 @@
         <v>9.8000000000000004E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="11">
         <v>40724</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="11">
         <v>40737</v>
       </c>
-      <c r="C4" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D4" s="10" t="s">
+      <c r="C4" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="1">
@@ -706,17 +699,17 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="11">
         <v>40816</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="11">
         <v>40834</v>
       </c>
-      <c r="C5" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D5" s="10" t="s">
+      <c r="C5" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="1">
@@ -729,17 +722,17 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="11">
         <v>40908</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="11">
         <v>40925</v>
       </c>
-      <c r="C6" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D6" s="10" t="s">
+      <c r="C6" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="1">
@@ -752,17 +745,17 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="11">
         <v>40999</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="11">
         <v>41012</v>
       </c>
-      <c r="C7" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D7" s="10" t="s">
+      <c r="C7" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E7" s="1">
@@ -775,17 +768,17 @@
         <v>8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="11">
         <v>41090</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="11">
         <v>41103</v>
       </c>
-      <c r="C8" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D8" s="10" t="s">
+      <c r="C8" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="1">
@@ -798,17 +791,17 @@
         <v>8.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="11">
         <v>41182</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="11">
         <v>41200</v>
       </c>
-      <c r="C9" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D9" s="10" t="s">
+      <c r="C9" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E9" s="1">
@@ -821,17 +814,17 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="11">
         <v>41274</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="11">
         <v>41292</v>
       </c>
-      <c r="C10" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D10" s="10" t="s">
+      <c r="C10" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E10" s="1">
@@ -844,17 +837,17 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="11">
         <v>41364</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="11">
         <v>41379</v>
       </c>
-      <c r="C11" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D11" s="10" t="s">
+      <c r="C11" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E11" s="1">
@@ -867,17 +860,17 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="11">
         <v>41455</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="11">
         <v>41470</v>
       </c>
-      <c r="C12" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D12" s="10" t="s">
+      <c r="C12" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E12" s="1">
@@ -890,17 +883,17 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="11">
         <v>41547</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="11">
         <v>41565</v>
       </c>
-      <c r="C13" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D13" s="10" t="s">
+      <c r="C13" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E13" s="1">
@@ -913,17 +906,17 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="11">
         <v>41639</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="11">
         <v>41659</v>
       </c>
-      <c r="C14" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D14" s="10" t="s">
+      <c r="C14" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E14" s="1">
@@ -936,17 +929,17 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="11">
         <v>41729</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="11">
         <v>41745</v>
       </c>
-      <c r="C15" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D15" s="10" t="s">
+      <c r="C15" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E15" s="1">
@@ -959,17 +952,17 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="11">
         <v>41820</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="11">
         <v>41836</v>
       </c>
-      <c r="C16" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D16" s="10" t="s">
+      <c r="C16" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E16" s="1">
@@ -982,17 +975,17 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="11">
         <v>41912</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="11">
         <v>41933</v>
       </c>
-      <c r="C17" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D17" s="10" t="s">
+      <c r="C17" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E17" s="1">
@@ -1005,17 +998,17 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="11">
         <v>42004</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="11">
         <v>42024</v>
       </c>
-      <c r="C18" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D18" s="10" t="s">
+      <c r="C18" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E18" s="1">
@@ -1028,17 +1021,17 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="11">
         <v>42094</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="11">
         <v>42109</v>
       </c>
-      <c r="C19" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D19" s="10" t="s">
+      <c r="C19" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E19" s="1">
@@ -1051,17 +1044,17 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="11">
         <v>42185</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="11">
         <v>42200</v>
       </c>
-      <c r="C20" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D20" s="10" t="s">
+      <c r="C20" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E20" s="1">
@@ -1074,17 +1067,17 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="11">
         <v>42277</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="11">
         <v>42296</v>
       </c>
-      <c r="C21" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D21" s="10" t="s">
+      <c r="C21" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E21" s="1">
@@ -1097,17 +1090,17 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="11">
         <v>42369</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="11">
         <v>42388</v>
       </c>
-      <c r="C22" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D22" s="10" t="s">
+      <c r="C22" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E22" s="1">
@@ -1120,17 +1113,17 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="11">
         <v>42460</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="11">
         <v>42475</v>
       </c>
-      <c r="C23" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D23" s="10" t="s">
+      <c r="C23" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E23" s="1">
@@ -1143,17 +1136,17 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="11">
         <v>42551</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="11">
         <v>42566</v>
       </c>
-      <c r="C24" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="C24" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E24" s="1">
@@ -1166,17 +1159,17 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="11">
         <v>42643</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="11">
         <v>42662</v>
       </c>
-      <c r="C25" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D25" s="10" t="s">
+      <c r="C25" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E25" s="1">
@@ -1189,17 +1182,17 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="11">
         <v>42735</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="11">
         <v>42755</v>
       </c>
-      <c r="C26" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D26" s="10" t="s">
+      <c r="C26" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E26" s="1">
@@ -1212,17 +1205,17 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="11">
         <v>42825</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="11">
         <v>42842</v>
       </c>
-      <c r="C27" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D27" s="10" t="s">
+      <c r="C27" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E27" s="1">
@@ -1235,17 +1228,17 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="11">
         <v>42916</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="11">
         <v>42933</v>
       </c>
-      <c r="C28" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D28" s="10" t="s">
+      <c r="C28" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E28" s="1">
@@ -1258,17 +1251,17 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="11">
         <v>43008</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="11">
         <v>43027</v>
       </c>
-      <c r="C29" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D29" s="10" t="s">
+      <c r="C29" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E29" s="1">
@@ -1281,17 +1274,17 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="11">
         <v>43100</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="11">
         <v>43118</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="6">
         <v>0.625</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E30" s="1">
@@ -1304,17 +1297,17 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="11">
         <v>43190</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="11">
         <v>43207</v>
       </c>
-      <c r="C31" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D31" s="10" t="s">
+      <c r="C31" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E31" s="1">
@@ -1327,17 +1320,17 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="11">
         <v>43281</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="11">
         <v>43297</v>
       </c>
-      <c r="C32" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D32" s="10" t="s">
+      <c r="C32" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D32" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E32" s="1">
@@ -1350,17 +1343,17 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="11">
         <v>43373</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="11">
         <v>43392</v>
       </c>
-      <c r="C33" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D33" s="10" t="s">
+      <c r="C33" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D33" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E33" s="1">
@@ -1373,17 +1366,17 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="11">
         <v>43465</v>
       </c>
-      <c r="B34" s="8">
+      <c r="B34" s="11">
         <v>43486</v>
       </c>
-      <c r="C34" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D34" s="10" t="s">
+      <c r="C34" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E34" s="1">
@@ -1396,17 +1389,17 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="11">
         <v>43555</v>
       </c>
-      <c r="B35" s="8">
+      <c r="B35" s="11">
         <v>43572</v>
       </c>
-      <c r="C35" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D35" s="10" t="s">
+      <c r="C35" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E35" s="1">
@@ -1419,17 +1412,17 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="11">
         <v>43646</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="11">
         <v>43661</v>
       </c>
-      <c r="C36" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D36" s="10" t="s">
+      <c r="C36" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D36" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E36" s="1">
@@ -1442,17 +1435,17 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="11">
         <v>43738</v>
       </c>
-      <c r="B37" s="8">
+      <c r="B37" s="11">
         <v>43756</v>
       </c>
-      <c r="C37" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D37" s="10" t="s">
+      <c r="C37" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D37" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E37" s="1">
@@ -1465,17 +1458,17 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="11">
         <v>43830</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B38" s="11">
         <v>43847</v>
       </c>
-      <c r="C38" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D38" s="10" t="s">
+      <c r="C38" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D38" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E38" s="1">
@@ -1488,17 +1481,17 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="11">
         <v>43921</v>
       </c>
-      <c r="B39" s="8">
+      <c r="B39" s="11">
         <v>43938</v>
       </c>
-      <c r="C39" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D39" s="10" t="s">
+      <c r="C39" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D39" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E39" s="1">
@@ -1511,17 +1504,17 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="11">
         <v>44012</v>
       </c>
-      <c r="B40" s="8">
+      <c r="B40" s="11">
         <v>44028</v>
       </c>
-      <c r="C40" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D40" s="10" t="s">
+      <c r="C40" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D40" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E40" s="1">
@@ -1534,17 +1527,17 @@
         <v>-6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="11">
         <v>44104</v>
       </c>
-      <c r="B41" s="8">
+      <c r="B41" s="11">
         <v>44123</v>
       </c>
-      <c r="C41" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D41" s="10" t="s">
+      <c r="C41" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D41" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E41" s="1">
@@ -1557,17 +1550,17 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="11">
         <v>44196</v>
       </c>
-      <c r="B42" s="8">
+      <c r="B42" s="11">
         <v>44214</v>
       </c>
-      <c r="C42" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D42" s="10" t="s">
+      <c r="C42" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D42" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E42" s="1">
@@ -1580,17 +1573,17 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="11">
         <v>44286</v>
       </c>
-      <c r="B43" s="8">
+      <c r="B43" s="11">
         <v>44302</v>
       </c>
-      <c r="C43" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D43" s="10" t="s">
+      <c r="C43" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D43" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E43" s="1">
@@ -1603,17 +1596,17 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="11">
         <v>44377</v>
       </c>
-      <c r="B44" s="8">
+      <c r="B44" s="11">
         <v>44392</v>
       </c>
-      <c r="C44" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D44" s="10" t="s">
+      <c r="C44" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D44" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E44" s="1">
@@ -1626,17 +1619,17 @@
         <v>0.183</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="11">
         <v>44469</v>
       </c>
-      <c r="B45" s="8">
+      <c r="B45" s="11">
         <v>44487</v>
       </c>
-      <c r="C45" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D45" s="10" t="s">
+      <c r="C45" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D45" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E45" s="1">
@@ -1649,17 +1642,17 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="11">
         <v>44561</v>
       </c>
-      <c r="B46" s="8">
+      <c r="B46" s="11">
         <v>44578</v>
       </c>
-      <c r="C46" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D46" s="10" t="s">
+      <c r="C46" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D46" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E46" s="1">
@@ -1672,17 +1665,17 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="11">
         <v>44651</v>
       </c>
-      <c r="B47" s="8">
+      <c r="B47" s="11">
         <v>44669</v>
       </c>
-      <c r="C47" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D47" s="10" t="s">
+      <c r="C47" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D47" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E47" s="1">
@@ -1695,17 +1688,17 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="11">
         <v>44742</v>
       </c>
-      <c r="B48" s="8">
+      <c r="B48" s="11">
         <v>44757</v>
       </c>
-      <c r="C48" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D48" s="10" t="s">
+      <c r="C48" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D48" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E48" s="1">
@@ -1718,17 +1711,17 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="11">
         <v>44834</v>
       </c>
-      <c r="B49" s="8">
+      <c r="B49" s="11">
         <v>44858</v>
       </c>
-      <c r="C49" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D49" s="10" t="s">
+      <c r="C49" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D49" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E49" s="1">
@@ -1741,17 +1734,17 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" s="11">
         <v>44926</v>
       </c>
-      <c r="B50" s="8">
+      <c r="B50" s="11">
         <v>44943</v>
       </c>
-      <c r="C50" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D50" s="10" t="s">
+      <c r="C50" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D50" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E50" s="1">
@@ -1764,17 +1757,17 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" s="11">
         <v>45016</v>
       </c>
-      <c r="B51" s="8">
+      <c r="B51" s="11">
         <v>45034</v>
       </c>
-      <c r="C51" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D51" s="10" t="s">
+      <c r="C51" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D51" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E51" s="1">
@@ -1787,17 +1780,17 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" s="11">
         <v>45107</v>
       </c>
-      <c r="B52" s="8">
+      <c r="B52" s="11">
         <v>45124</v>
       </c>
-      <c r="C52" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D52" s="10" t="s">
+      <c r="C52" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D52" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E52" s="1">
@@ -1810,17 +1803,17 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" s="11">
         <v>45199</v>
       </c>
-      <c r="B53" s="8">
+      <c r="B53" s="11">
         <v>45217</v>
       </c>
-      <c r="C53" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D53" s="10" t="s">
+      <c r="C53" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D53" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E53" s="1">
@@ -1833,17 +1826,17 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="11">
         <v>45291</v>
       </c>
-      <c r="B54" s="8">
+      <c r="B54" s="11">
         <v>45308</v>
       </c>
-      <c r="C54" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D54" s="10" t="s">
+      <c r="C54" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D54" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E54" s="1">
@@ -1856,17 +1849,17 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" s="7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="11">
         <v>45382</v>
       </c>
-      <c r="B55" s="8">
+      <c r="B55" s="11">
         <v>45398</v>
       </c>
-      <c r="C55" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D55" s="10" t="s">
+      <c r="C55" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D55" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E55" s="1">
@@ -1879,17 +1872,17 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" s="7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="11">
         <v>45473</v>
       </c>
-      <c r="B56" s="8">
+      <c r="B56" s="11">
         <v>45488</v>
       </c>
-      <c r="C56" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D56" s="10" t="s">
+      <c r="C56" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D56" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E56" s="1">
@@ -1902,17 +1895,17 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="11">
         <v>45565</v>
       </c>
-      <c r="B57" s="8">
+      <c r="B57" s="11">
         <v>45583</v>
       </c>
-      <c r="C57" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D57" s="10" t="s">
+      <c r="C57" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D57" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E57" s="1">
@@ -1925,17 +1918,17 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="11">
         <v>45657</v>
       </c>
-      <c r="B58" s="8">
+      <c r="B58" s="11">
         <v>45674</v>
       </c>
-      <c r="C58" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D58" s="10" t="s">
+      <c r="C58" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D58" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E58" s="1">
@@ -1948,17 +1941,17 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="11">
         <v>45747</v>
       </c>
-      <c r="B59" s="8">
+      <c r="B59" s="11">
         <v>45763</v>
       </c>
-      <c r="C59" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D59" s="10" t="s">
+      <c r="C59" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D59" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E59" s="1">
@@ -1971,17 +1964,17 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="11">
         <v>45838</v>
       </c>
-      <c r="B60" s="8">
+      <c r="B60" s="11">
         <v>45853</v>
       </c>
-      <c r="C60" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D60" s="10" t="s">
+      <c r="C60" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D60" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E60" s="1">
@@ -1991,17 +1984,17 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="11">
         <v>45930</v>
       </c>
-      <c r="B61" s="8">
+      <c r="B61" s="11">
         <v>45950</v>
       </c>
-      <c r="C61" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D61" s="10" t="s">
+      <c r="C61" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D61" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E61" s="1">
@@ -2014,17 +2007,17 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" s="11">
         <v>46022</v>
       </c>
-      <c r="B62" s="8">
+      <c r="B62" s="11">
         <v>46041</v>
       </c>
-      <c r="C62" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D62" s="10" t="s">
+      <c r="C62" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D62" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E62" s="1">
@@ -2037,17 +2030,17 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="11">
         <v>46112</v>
       </c>
-      <c r="B63" s="8">
+      <c r="B63" s="11">
         <v>46128</v>
       </c>
-      <c r="C63" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D63" s="10" t="s">
+      <c r="C63" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D63" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E63" s="1">
@@ -2060,17 +2053,17 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" s="11">
         <v>46203</v>
       </c>
-      <c r="B64" s="8">
+      <c r="B64" s="11">
         <v>46218</v>
       </c>
-      <c r="C64" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D64" s="10" t="s">
+      <c r="C64" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D64" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E64" s="1">
